--- a/data/trans_orig/IP05A04-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP05A04-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>85423</t>
+          <t>85394</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96198</t>
+          <t>96606</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>97856</t>
+          <t>97041</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>110024</t>
+          <t>109397</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187938</t>
+          <t>188141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>203876</t>
+          <t>203870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7405</t>
+          <t>7049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17713</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18012</t>
+          <t>17968</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33478</t>
+          <t>33097</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4930</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5164</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>694</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6953</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>206391</t>
+          <t>205541</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>223422</t>
+          <t>223230</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>215640</t>
+          <t>215125</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231004</t>
+          <t>230461</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>426386</t>
+          <t>427257</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>449791</t>
+          <t>450260</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,2%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19424</t>
+          <t>19411</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35544</t>
+          <t>36292</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14834</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28931</t>
+          <t>29140</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>37464</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>59269</t>
+          <t>59162</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10279</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3293</t>
+          <t>2858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11430</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6998</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>17825</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>101805</t>
+          <t>100919</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>114288</t>
+          <t>113837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>117057</t>
+          <t>116283</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129151</t>
+          <t>129208</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>221922</t>
+          <t>222801</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>239993</t>
+          <t>240608</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10650</t>
+          <t>11002</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22836</t>
+          <t>23646</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10022</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>22612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24619</t>
+          <t>23865</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41228</t>
+          <t>40654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4950</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4612</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>165561</t>
+          <t>166440</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>179713</t>
+          <t>180498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>177816</t>
+          <t>178608</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>191703</t>
+          <t>192187</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>349207</t>
+          <t>349221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>367917</t>
+          <t>368467</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11072</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>23661</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19893</t>
+          <t>19499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21779</t>
+          <t>22154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38714</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>736</t>
+          <t>795</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>2641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9908</t>
+          <t>9993</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>14715</t>
+          <t>14600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2417,7 +2417,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,67%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>573912</t>
+          <t>574508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>602258</t>
+          <t>603460</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>623553</t>
+          <t>623906</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>650370</t>
+          <t>650920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1208496</t>
+          <t>1208356</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1248268</t>
+          <t>1245957</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,75%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59322</t>
+          <t>58701</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>85534</t>
+          <t>84795</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51623</t>
+          <t>51704</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75856</t>
+          <t>75869</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>116951</t>
+          <t>116636</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>152418</t>
+          <t>152062</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7026</t>
+          <t>6723</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17965</t>
+          <t>18730</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9376</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21161</t>
+          <t>21619</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>19156</t>
+          <t>18814</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35935</t>
+          <t>34876</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>130453</t>
+          <t>130302</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>140302</t>
+          <t>140672</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126707</t>
+          <t>127385</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>137714</t>
+          <t>138109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>261320</t>
+          <t>261516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>276024</t>
+          <t>276241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4175</t>
+          <t>4013</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13089</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3373,12 +3373,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4575</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14332</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10481</t>
+          <t>10601</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24088</t>
+          <t>23596</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>575</t>
+          <t>582</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>5620</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>6745</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>9129</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>210324</t>
+          <t>209506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>223889</t>
+          <t>223787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236787</t>
+          <t>237849</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>252811</t>
+          <t>252583</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>452911</t>
+          <t>452940</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>474353</t>
+          <t>473631</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,83%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>8376</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20619</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>13614</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27948</t>
+          <t>27828</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>24563</t>
+          <t>24406</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>42982</t>
+          <t>43540</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8365</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7584</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,47 +3977,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>2,82%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>7729</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>13507</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>2,68%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>7729</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>4201</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>13912</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138123</t>
+          <t>138765</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149098</t>
+          <t>149229</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>139297</t>
+          <t>138728</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150093</t>
+          <t>149794</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>281474</t>
+          <t>281665</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>296752</t>
+          <t>296853</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16118</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4681</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13717</t>
+          <t>14136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>12987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26518</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>758</t>
+          <t>693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6772</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1390</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2907</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>11306</t>
+          <t>10868</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152877</t>
+          <t>152686</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>163484</t>
+          <t>163175</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>153761</t>
+          <t>153580</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>166629</t>
+          <t>166831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>309697</t>
+          <t>310856</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>326941</t>
+          <t>327371</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11899</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11052</t>
+          <t>10636</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>23441</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16350</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>31343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,0%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1419</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7439</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>636</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>4683</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2727</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10562</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>646380</t>
+          <t>646724</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>667901</t>
+          <t>667802</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>672015</t>
+          <t>671651</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>697058</t>
+          <t>697178</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1325130</t>
+          <t>1323890</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1360383</t>
+          <t>1358863</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>29494</t>
+          <t>29497</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49277</t>
+          <t>47842</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65044</t>
+          <t>66392</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>75769</t>
+          <t>77454</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>107377</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,37%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18956</t>
+          <t>18598</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6982</t>
+          <t>6978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18984</t>
+          <t>19053</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17270</t>
+          <t>16411</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>33690</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>112324</t>
+          <t>112694</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122946</t>
+          <t>123022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105080</t>
+          <t>105529</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115803</t>
+          <t>115949</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>221059</t>
+          <t>220804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>236560</t>
+          <t>236846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>13282</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6051</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>15723</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>13060</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>26033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,2%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>645</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,89%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179109</t>
+          <t>179151</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>192907</t>
+          <t>192674</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>224223</t>
+          <t>224647</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>239881</t>
+          <t>239460</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409147</t>
+          <t>406487</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>429213</t>
+          <t>428275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11167</t>
+          <t>11080</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23831</t>
+          <t>23280</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,82 +6341,82 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
+          <t>5,29%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>11,12%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>16622</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>10890</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>23999</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>4,22%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>32964</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>24975</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>43256</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>5,34%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>11,39%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>16622</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>10773</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>23570</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>6,44%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>32964</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>25034</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>43105</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2976</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14603</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>21584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>165623</t>
+          <t>164836</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>177298</t>
+          <t>177103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>157429</t>
+          <t>157665</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>171867</t>
+          <t>172679</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327712</t>
+          <t>327859</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>346714</t>
+          <t>347101</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,43%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14989</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8522</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>19898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16119</t>
+          <t>16021</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31662</t>
+          <t>30986</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>10805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4770</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>14436</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9303</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>21842</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>148152</t>
+          <t>148167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>161108</t>
+          <t>160681</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>149054</t>
+          <t>148453</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>161856</t>
+          <t>162481</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>302831</t>
+          <t>302223</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>320376</t>
+          <t>320549</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7299</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17862</t>
+          <t>17606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7851</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>16893</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>32667</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8646</t>
+          <t>8636</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7391,7 +7391,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>619370</t>
+          <t>620090</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>644709</t>
+          <t>643246</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>652796</t>
+          <t>651138</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>679181</t>
+          <t>678489</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1279691</t>
+          <t>1280034</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1315677</t>
+          <t>1316402</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,33%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>35644</t>
+          <t>36739</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>56944</t>
+          <t>56323</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41033</t>
+          <t>42609</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64103</t>
+          <t>64958</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>83754</t>
+          <t>82953</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>114016</t>
+          <t>115230</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14416</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29193</t>
+          <t>28852</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16328</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>31218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7862,7 +7862,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>33663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54376</t>
+          <t>54957</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51115</t>
+          <t>51434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>56360</t>
+          <t>56326</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52342</t>
+          <t>51842</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59185</t>
+          <t>59214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106804</t>
+          <t>106128</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114615</t>
+          <t>114909</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4523</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>1146</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2433</t>
+          <t>2494</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9751</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8500,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4300</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>381</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4053</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>605</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145930</t>
+          <t>145724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153949</t>
+          <t>153994</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165655</t>
+          <t>164461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176313</t>
+          <t>176350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>315171</t>
+          <t>314734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>328492</t>
+          <t>327820</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,72%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1760</t>
+          <t>1729</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7628</t>
+          <t>8267</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>3704</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13242</t>
+          <t>14182</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>7392</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>18679</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>771</t>
+          <t>779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6867</t>
+          <t>7172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8991,7 +8991,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9006,7 +9006,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1958</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9923</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -9181,12 +9181,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>159982</t>
+          <t>160120</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>169313</t>
+          <t>169722</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9196,12 +9196,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>196520</t>
+          <t>197697</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>207862</t>
+          <t>208216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>361982</t>
+          <t>361676</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375778</t>
+          <t>375791</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,5%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12344</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2859</t>
+          <t>2613</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13805</t>
+          <t>12505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7716</t>
+          <t>7318</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20497</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -9412,7 +9412,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4901</t>
+          <t>5195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9462,7 +9462,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>800</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9497,7 +9497,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>257444</t>
+          <t>257411</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>269376</t>
+          <t>269014</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>283257</t>
+          <t>281836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>297633</t>
+          <t>297152</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>544068</t>
+          <t>545744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>563831</t>
+          <t>563812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12169</t>
+          <t>12605</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3881</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16373</t>
+          <t>16345</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9800,12 +9800,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9107</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24261</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>785</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8231</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1876</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11481</t>
+          <t>12614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15483</t>
+          <t>15693</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,71%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>625845</t>
+          <t>625985</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>643144</t>
+          <t>643683</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>711773</t>
+          <t>711808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>734682</t>
+          <t>734022</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1345484</t>
+          <t>1344876</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1372326</t>
+          <t>1373396</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,54%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13377</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27689</t>
+          <t>26577</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36344</t>
+          <t>35715</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34567</t>
+          <t>33621</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>58235</t>
+          <t>57244</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>15657</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,82 +10334,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>9633</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>4871</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>16972</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
           <t>2,23%</t>
         </is>
       </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>9633</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>5229</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>17143</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>18039</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>11695</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>27136</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>1,27%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>18039</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>11517</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>27272</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
